--- a/data/demo/Договоры 2026.xlsx
+++ b/data/demo/Договоры 2026.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Базовый договор (внебюджет)</t>
+          <t>Внебюджетный договор НИР «Стенд-26»</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>НИР</t>
+          <t>внебюджет</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5720000</v>
+        <v>7000000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -639,21 +639,17 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Отдел 12</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C_P4-26</t>
+          <t>C_COM-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Договор с надбавкой за интенсивность</t>
+          <t>Коммерческий договор ОКР «Привод-26»</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -663,7 +659,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>НИР</t>
+          <t>коммерческий</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -687,7 +683,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1800000</v>
+        <v>1300000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -696,12 +692,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -744,11 +740,7 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Отдел 12</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -768,7 +760,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>НИР</t>
+          <t>госзаказ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -792,7 +784,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3264000</v>
+        <v>3592352</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -801,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -849,11 +841,7 @@
           <t>31.10.2026</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Лаборатория 3</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -873,7 +861,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>НИР</t>
+          <t>грант</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -888,7 +876,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01.06.2026</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,7 +885,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1330000</v>
+        <v>1560000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -906,7 +894,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -954,11 +942,108 @@
           <t>31.12.2026</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Лаборатория 3</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C_PRI-26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Программа «Приоритет 2030», проект «Цифровой двойник»</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>П-2030/26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>приоритет</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20576У17450</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01.01.2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -971,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,16 +1133,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>700000</v>
+        <v>950000</v>
       </c>
       <c r="C2" t="n">
-        <v>700000</v>
+        <v>950000</v>
       </c>
       <c r="D2" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="E2" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="F2" t="n">
         <v>400000</v>
@@ -1078,53 +1163,53 @@
         <v>400000</v>
       </c>
       <c r="L2" t="n">
-        <v>560000</v>
+        <v>850000</v>
       </c>
       <c r="M2" t="n">
-        <v>560000</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C_P4-26</t>
+          <t>C_COM-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
       <c r="C3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
       <c r="F3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
       <c r="I3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
       <c r="L3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1140,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1632000</v>
+        <v>1500000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1149,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1632000</v>
+        <v>1200000</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1158,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>892352</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1189,27 +1274,70 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>760000</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>570000</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C_PRI-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
